--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00741B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00741B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51511828-F5C8-43E0-8E22-72A81E96FADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E354CA2C-A4E6-486A-A039-60E5ECB64C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{70A90325-8E64-4DD4-A9A3-9DBAC8D7D9F9}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{96656155-EE33-4DEB-81C7-01F6190EF35C}"/>
   </bookViews>
   <sheets>
     <sheet name="00741B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1696,24 +1696,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{930DFC72-32B2-4ED8-AD1D-E58E7EF237DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7920CF35-2908-42D3-92ED-9A314538EE92}">
   <dimension ref="A1:R56"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1741,7 +1742,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1771,7 +1772,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1817,7 +1818,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1867,7 +1868,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1921,7 +1922,7 @@
         <v>6.32</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1947,7 +1948,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -2003,7 +2004,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -2059,7 +2060,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>2025</v>
       </c>
@@ -2113,7 +2114,7 @@
         <v>6.66</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -2169,7 +2170,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2225,7 +2226,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2281,7 +2282,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2337,7 +2338,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2393,7 +2394,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2449,7 +2450,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2505,7 +2506,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>26</v>
       </c>
@@ -2561,7 +2562,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>26</v>
       </c>
@@ -2617,7 +2618,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>26</v>
       </c>
@@ -2673,7 +2674,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2729,7 +2730,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
@@ -2785,7 +2786,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="51">
         <v>2024</v>
       </c>
@@ -2839,7 +2840,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2895,7 +2896,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2951,7 +2952,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -3007,7 +3008,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -3063,7 +3064,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -3119,7 +3120,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -3175,7 +3176,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3231,7 +3232,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>26</v>
       </c>
@@ -3287,7 +3288,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="49">
         <v>2023</v>
       </c>
@@ -3341,7 +3342,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>26</v>
       </c>
@@ -3397,7 +3398,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
         <v>26</v>
       </c>
@@ -3453,7 +3454,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
         <v>26</v>
       </c>
@@ -3509,7 +3510,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
         <v>26</v>
       </c>
@@ -3565,7 +3566,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="51">
         <v>2022</v>
       </c>
@@ -3619,7 +3620,7 @@
         <v>6.51</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>26</v>
       </c>
@@ -3675,7 +3676,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>26</v>
       </c>
@@ -3731,7 +3732,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>26</v>
       </c>
@@ -3787,7 +3788,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>26</v>
       </c>
@@ -3843,7 +3844,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="49">
         <v>2021</v>
       </c>
@@ -3897,7 +3898,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>26</v>
       </c>
@@ -3953,7 +3954,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
         <v>26</v>
       </c>
@@ -4009,7 +4010,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
         <v>26</v>
       </c>
@@ -4065,7 +4066,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
         <v>26</v>
       </c>
@@ -4121,7 +4122,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="51">
         <v>2020</v>
       </c>
@@ -4175,7 +4176,7 @@
         <v>4.87</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>26</v>
       </c>
@@ -4231,7 +4232,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
         <v>26</v>
       </c>
@@ -4287,7 +4288,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>26</v>
       </c>
@@ -4343,7 +4344,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
         <v>26</v>
       </c>
@@ -4399,7 +4400,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="49">
         <v>2019</v>
       </c>
@@ -4453,7 +4454,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
         <v>26</v>
       </c>
@@ -4509,7 +4510,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
         <v>26</v>
       </c>
@@ -4565,7 +4566,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
         <v>26</v>
       </c>
@@ -4621,7 +4622,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
         <v>26</v>
       </c>
@@ -4677,7 +4678,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="51" t="s">
         <v>103</v>
       </c>
